--- a/course-content/security-tutor/CEH-readiness-AAK.xlsx
+++ b/course-content/security-tutor/CEH-readiness-AAK.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <calcPr fullCalcOnLoad="1"/>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Checkpoint 1" sheetId="2" r:id="rId2"/>
     <sheet name="Domain Coverage" sheetId="3" r:id="rId3"/>
   </sheets>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 

--- a/course-content/security-tutor/CEH-readiness-AAK.xlsx
+++ b/course-content/security-tutor/CEH-readiness-AAK.xlsx
@@ -5,6 +5,7 @@
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
     <sheet name="Checkpoint 1" sheetId="2" r:id="rId2"/>
     <sheet name="Domain Coverage" sheetId="3" r:id="rId3"/>
+    <sheet name="Checkpoint 2" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
@@ -120,7 +121,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -159,6 +160,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
 </styleSheet>
 </file>
@@ -248,18 +252,31 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
-      <c r="B6" s="10"/>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(add when Checkpoint 2 sheet is created)</t>
-        </is>
-      </c>
-      <c r="D6" s="10"/>
-      <c r="E6" s="10"/>
-      <c r="F6" s="10"/>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-10-25</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Days 12-19 (Phase 4 Web Security: IDOR, SQLi, XSS, CSRF, CORS, SSRF, Session Fixation, Cookie Security, Origin-vs-Site) + carried-over re-probes</t>
+        </is>
+      </c>
+      <c r="D6" s="5">
+        <f>'Checkpoint 2'!H2</f>
+        <v>12</v>
+      </c>
+      <c r="E6" s="5">
+        <f>'Checkpoint 2'!I2</f>
+        <v>8</v>
+      </c>
+      <c r="F6" s="6">
+        <f>IFERROR(E6/D6,"")</f>
+        <v>0.6666666666666666</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="10">
@@ -331,6 +348,13 @@
         </is>
       </c>
     </row>
+    <row r="15" ht="60" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checkpoint 2: Exam-ready on Phase 4 (Web Security) domains overall - strong, often-unprompted reasoning on Broken Access Control, SQLi, CSRF/SSRF, Session Fixation, HttpOnly, and Origin-vs-Site. Two items needed one nudge to reach full precision (CORS preflight header names, SSRF/IMDS value). Two items still flagged for re-check: nmap filtered-vs-closed (missed a third time - recommend a real packet-capture demo next time, not another verbal re-check) and SameSite=Lax mechanics (right outcome, reasoning corrected live - one more light confirmation planned).</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
       <c r="A16" s="7" t="inlineStr">
         <is>
@@ -360,10 +384,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A15:F15"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A18:F18"/>
     <mergeCell ref="A19:F19"/>
@@ -1236,4 +1261,415 @@
     <mergeCell ref="A2:D2"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <cols>
+    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="60" customWidth="1"/>
+    <col min="4" max="4" width="26" customWidth="1"/>
+    <col min="5" max="5" width="70" customWidth="1"/>
+    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="9" max="9" width="20" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Checkpoint 2 — 2026-10-25 (Day 20) — Days 12-19 Review</t>
+        </is>
+      </c>
+      <c r="H1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Questions (for Summary link)</t>
+        </is>
+      </c>
+      <c r="I1" s="9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct (for Summary link)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12 CEH-style questions/items, Days 12-19 scope (Phase 4 Web Security) plus carried-over re-probes. Qualitative readiness read rather than a strict score: items below are grouped Full marks / Correct after one nudge / Still shaky, reconstructed from the session's progress notes rather than a verbatim per-question transcript.</t>
+        </is>
+      </c>
+      <c r="H2" s="0">
+        <f>E18</f>
+        <v>12</v>
+      </c>
+      <c r="I2" s="0">
+        <f>F18</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">#</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Domain</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Item / Topic</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Result</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5">
+        <v>1</v>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - Access Control</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Broken Access Control / IDOR (authn vs authz distinction, derived unprompted)</t>
+        </is>
+      </c>
+      <c r="D5" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correctly derived the authentication-vs-authorization distinction without being told the term.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - SQL Injection</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SQL injection mechanics (UNION/blind concepts)</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reconfirmed solid from Day 13.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5">
+        <v>3</v>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - CSRF/SSRF</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSRF vs SSRF: "who sends the forged request"</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Clean distinction between victim's browser (CSRF) and server (SSRF).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - Session Attacks</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Session Fixation root cause + fix</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Named session regeneration on login/logout/password change unprompted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5">
+        <v>5</v>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - Cookie Security</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">HttpOnly scoping</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fully resolved after earlier light re-check pattern; no gap remaining.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - Origin vs Site</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Origin-vs-site distinction on a new example (app.example.com:8443 vs api.example.com:8443)</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Applied cleanly and unprompted to a brand-new example.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5">
+        <v>7</v>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - CORS</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CORS preflight header names</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct after one nudge</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct concept, imprecise on exact header names on first pass; reached full precision after a nudge.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5">
+        <v>8</v>
+      </c>
+      <c r="B12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cloud / SSRF</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SSRF / IMDS value explanation</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Correct after one nudge</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Credentials-theft rationale and link-local addressing rationale needed prompting to state precisely.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5">
+        <v>9</v>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Recon - nmap</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">nmap filtered vs. closed port states</t>
+        </is>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Still shaky (missed 3rd time)</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Conflated 'filtered' with HTTP 404 semantics before self-correcting. Also missed at Checkpoint 1. High-priority: plan a real packet-capture demo next time instead of another verbal re-check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5">
+        <v>10</v>
+      </c>
+      <c r="B14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - Cookie Security</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">SameSite=Lax mechanics (top-level navigation vs. embedded request)</t>
+        </is>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Still shaky (reasoning gap)</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Had the right outcome (POST blocked, GET-link allowed) but wrong reasoning (attributed to subresource loading, not top-level-navigation vs. embedded-request). Corrected live with a comparison table; one more light check recommended.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5">
+        <v>11</v>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - XSS</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reflected XSS (re-tested conceptually)</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Covered as part of Phase 4 reconfirmation; no new gap surfaced this checkpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5">
+        <v>12</v>
+      </c>
+      <c r="B16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Web App Security - CSRF</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CSRF defenses (re-tested conceptually)</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Covered as part of Phase 4 reconfirmation; no new gap surfaced this checkpoint.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTALS</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Items:</t>
+        </is>
+      </c>
+      <c r="E18" s="5">
+        <f>COUNTA(A5:A16)</f>
+        <v>12</v>
+      </c>
+      <c r="F18" s="5">
+        <f>COUNTIF(D5:D16,"Full marks")</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="D19" s="15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Full marks / Nudge / Still shaky:</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8 / 2 / 2</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A2:E2"/>
+  </mergeCells>
+</worksheet>
 </file>